--- a/artfynd/A 36131-2025 artfynd.xlsx
+++ b/artfynd/A 36131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127503271</v>
       </c>
       <c r="B2" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36131-2025 artfynd.xlsx
+++ b/artfynd/A 36131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127503271</v>
       </c>
       <c r="B2" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36131-2025 artfynd.xlsx
+++ b/artfynd/A 36131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127503271</v>
       </c>
       <c r="B2" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127505492</v>
       </c>
       <c r="B3" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127506993</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36131-2025 artfynd.xlsx
+++ b/artfynd/A 36131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127503271</v>
       </c>
       <c r="B2" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127505492</v>
       </c>
       <c r="B3" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36131-2025 artfynd.xlsx
+++ b/artfynd/A 36131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127503271</v>
       </c>
       <c r="B2" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127505492</v>
       </c>
       <c r="B3" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127506993</v>
       </c>
       <c r="B4" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36131-2025 artfynd.xlsx
+++ b/artfynd/A 36131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127503271</v>
       </c>
       <c r="B2" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127505492</v>
       </c>
       <c r="B3" t="n">
-        <v>95779</v>
+        <v>95787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127506993</v>
       </c>
       <c r="B4" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36131-2025 artfynd.xlsx
+++ b/artfynd/A 36131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127503271</v>
       </c>
       <c r="B2" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127505492</v>
       </c>
       <c r="B3" t="n">
-        <v>95787</v>
+        <v>95788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36131-2025 artfynd.xlsx
+++ b/artfynd/A 36131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127503271</v>
       </c>
       <c r="B2" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127505492</v>
       </c>
       <c r="B3" t="n">
-        <v>95788</v>
+        <v>95789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36131-2025 artfynd.xlsx
+++ b/artfynd/A 36131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127503271</v>
       </c>
       <c r="B2" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127505492</v>
       </c>
       <c r="B3" t="n">
-        <v>95789</v>
+        <v>95790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
